--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -13,7 +13,8 @@
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
-    <sheet name="技能" sheetId="2" r:id="rId2"/>
+    <sheet name="红装" sheetId="3" r:id="rId2"/>
+    <sheet name="技能" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -144,6 +145,64 @@
         </r>
       </text>
     </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 均匀随机
+2 线性增伤随机
+3 指数增伤随机</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="M4" authorId="1">
       <text>
         <r>
@@ -173,7 +232,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -326,6 +385,21 @@
   </si>
   <si>
     <t>道伤加成</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>全技能等级增加</t>
@@ -1043,6 +1117,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4441,6 +4516,1438 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="C1:O38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="7" width="13" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1666666666667" style="1" customWidth="1"/>
+    <col min="9" max="14" width="13" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="1">
+        <v>16</v>
+      </c>
+      <c r="J6" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>20</v>
+      </c>
+      <c r="M6" s="1">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1">
+        <v>16</v>
+      </c>
+      <c r="J7" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>20</v>
+      </c>
+      <c r="M7" s="1">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="1">
+        <v>16</v>
+      </c>
+      <c r="J8" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>20</v>
+      </c>
+      <c r="M8" s="1">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1">
+        <v>16</v>
+      </c>
+      <c r="J9" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>20</v>
+      </c>
+      <c r="M9" s="1">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="1">
+        <v>16</v>
+      </c>
+      <c r="J10" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>20</v>
+      </c>
+      <c r="M10" s="1">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="1">
+        <v>16</v>
+      </c>
+      <c r="J11" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>20</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="1">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>60</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="1">
+        <v>11</v>
+      </c>
+      <c r="J13" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>60</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="1">
+        <v>11</v>
+      </c>
+      <c r="J14" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>40</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>20</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="1">
+        <v>11</v>
+      </c>
+      <c r="J15" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>60</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C16" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="1">
+        <v>11</v>
+      </c>
+      <c r="J16" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>40</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C19" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>100</v>
+      </c>
+      <c r="K19" s="1">
+        <v>10</v>
+      </c>
+      <c r="L19" s="3">
+        <v>300</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C20" s="1">
+        <v>1102</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>100</v>
+      </c>
+      <c r="K20" s="1">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="1">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C21" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>100</v>
+      </c>
+      <c r="K21" s="1">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
+        <v>300</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C22" s="1">
+        <v>1104</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>21</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>100</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="1">
+        <v>2</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20</v>
+      </c>
+      <c r="G23" s="1">
+        <v>80</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>100</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
+        <v>100</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C24" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>27</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>100</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>28</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5</v>
+      </c>
+      <c r="G25" s="1">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>100</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3">
+        <v>100</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>81</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>100</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="3">
+        <v>100</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="1">
+        <v>1109</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>82</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>100</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="3">
+        <v>100</v>
+      </c>
+      <c r="M27" s="1">
+        <v>2</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>83</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>100</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>100</v>
+      </c>
+      <c r="M28" s="1">
+        <v>2</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>84</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>100</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3">
+        <v>100</v>
+      </c>
+      <c r="M29" s="1">
+        <v>2</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F30" s="1">
+        <v>20</v>
+      </c>
+      <c r="G30" s="1">
+        <v>100</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>100</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
+      <c r="L30" s="3">
+        <v>100</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="1">
+        <v>1113</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1">
+        <v>50</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>100</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3</v>
+      </c>
+      <c r="L31" s="3">
+        <v>100</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="1">
+        <v>1114</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F32" s="1">
+        <v>5</v>
+      </c>
+      <c r="G32" s="1">
+        <v>30</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>100</v>
+      </c>
+      <c r="K32" s="1">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="1">
+        <v>1115</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>50</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>100</v>
+      </c>
+      <c r="K33" s="1">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
+        <v>100</v>
+      </c>
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="1">
+        <v>1116</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1005</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>50</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>100</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="3">
+        <v>100</v>
+      </c>
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
+        <v>2</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="1">
+        <v>1117</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1006</v>
+      </c>
+      <c r="F35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
+        <v>50</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
+        <v>100</v>
+      </c>
+      <c r="K35" s="1">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
+        <v>100</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1">
+        <v>3</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="1">
+        <v>1118</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1007</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>50</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1">
+        <v>100</v>
+      </c>
+      <c r="K36" s="1">
+        <v>2</v>
+      </c>
+      <c r="L36" s="3">
+        <v>100</v>
+      </c>
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="1">
+        <v>1119</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1008</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>50</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>100</v>
+      </c>
+      <c r="K37" s="1">
+        <v>2</v>
+      </c>
+      <c r="L37" s="3">
+        <v>100</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
+        <v>2</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C38" s="1">
+        <v>1120</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1009</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1">
+        <v>50</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>100</v>
+      </c>
+      <c r="K38" s="1">
+        <v>2</v>
+      </c>
+      <c r="L38" s="3">
+        <v>100</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
+        <v>3</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 O3:O5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:O27"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
@@ -4619,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4660,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4701,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4742,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4783,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4824,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4865,7 +6372,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4906,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4947,7 +6454,7 @@
         <v>2</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -4988,7 +6495,7 @@
         <v>2</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="3:15">
@@ -5029,7 +6536,7 @@
         <v>2</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="3:15">
@@ -5070,7 +6577,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="3:15">
@@ -5111,7 +6618,7 @@
         <v>2</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="3:15">
@@ -5152,7 +6659,7 @@
         <v>2</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="3:15">
@@ -5193,7 +6700,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="3:15">
@@ -5234,7 +6741,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="3:15">
@@ -5275,7 +6782,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="3:15">
@@ -5316,7 +6823,7 @@
         <v>3</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="3:15">
@@ -5357,7 +6864,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="3:15">
@@ -5398,7 +6905,7 @@
         <v>3</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="3:15">
@@ -5439,7 +6946,7 @@
         <v>3</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="3:15">
@@ -5480,7 +6987,7 @@
         <v>3</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -232,7 +232,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -387,19 +387,19 @@
     <t>道伤加成</t>
   </si>
   <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>5,7</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>全技能等级增加</t>
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -1629,7 +1629,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>7</v>
@@ -1670,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>8</v>
@@ -1711,7 +1711,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>8</v>
@@ -1752,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
@@ -1793,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>8</v>
@@ -4516,7 +4516,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O38"/>
+  <dimension ref="C1:O32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4664,25 +4664,25 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J6" s="1">
         <v>99999</v>
@@ -4691,39 +4691,39 @@
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="1">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J7" s="1">
         <v>99999</v>
@@ -4732,39 +4732,39 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J8" s="1">
         <v>99999</v>
@@ -4773,39 +4773,39 @@
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="1">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I9" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J9" s="1">
         <v>99999</v>
@@ -4814,39 +4814,39 @@
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
       </c>
       <c r="E10" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I10" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1">
         <v>99999</v>
@@ -4855,253 +4855,171 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" s="1">
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C11" s="1">
-        <v>1006</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>3</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="1">
-        <v>16</v>
-      </c>
-      <c r="J11" s="1">
-        <v>99999</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>20</v>
-      </c>
-      <c r="M11" s="1">
-        <v>3</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C12" s="1">
-        <v>1007</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5</v>
-      </c>
-      <c r="G12" s="1">
-        <v>20</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="1">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <v>99999</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>60</v>
-      </c>
-      <c r="M12" s="1">
-        <v>2</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
-        <v>1008</v>
+        <v>1101</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
       </c>
       <c r="E13" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="G13" s="1">
-        <v>20</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>53</v>
+        <v>50000</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I13" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1">
-        <v>99999</v>
+        <v>100</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="L13" s="3">
+        <v>300</v>
       </c>
       <c r="M13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
-        <v>1009</v>
+        <v>1102</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
       <c r="E14" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="1">
-        <v>10</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>54</v>
+        <v>10000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I14" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
-        <v>99999</v>
+        <v>100</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
+        <v>300</v>
       </c>
       <c r="M14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
-        <v>1010</v>
+        <v>1103</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="1">
-        <v>20</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>52</v>
+        <v>10000</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I15" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1">
-        <v>99999</v>
+        <v>100</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="L15" s="3">
+        <v>300</v>
       </c>
       <c r="M15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1">
-        <v>1011</v>
+        <v>1104</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I16" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1">
-        <v>99999</v>
+        <v>100</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="1">
-        <v>40</v>
+      <c r="L16" s="3">
+        <v>100</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
@@ -5110,27 +5028,109 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C17" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>22</v>
+      </c>
+      <c r="F17" s="1">
+        <v>20</v>
+      </c>
+      <c r="G17" s="1">
+        <v>80</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>100</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C18" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>100</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="1">
+        <v>2</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="1">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F19" s="1">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>50000</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -5139,36 +5139,36 @@
         <v>100</v>
       </c>
       <c r="K19" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="1">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
       <c r="E20" s="1">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="F20" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
@@ -5180,36 +5180,36 @@
         <v>100</v>
       </c>
       <c r="K20" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="1">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="F21" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
@@ -5221,39 +5221,39 @@
         <v>100</v>
       </c>
       <c r="K21" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="1">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>51</v>
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -5274,27 +5274,27 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="1">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F23" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>80</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
@@ -5315,27 +5315,27 @@
         <v>0</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
       </c>
       <c r="E24" s="1">
-        <v>27</v>
+        <v>1001</v>
       </c>
       <c r="F24" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G24" s="1">
-        <v>20</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -5344,39 +5344,39 @@
         <v>100</v>
       </c>
       <c r="K24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" s="1">
         <v>0</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>28</v>
+        <v>1002</v>
       </c>
       <c r="F25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25" s="1">
-        <v>20</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -5385,36 +5385,36 @@
         <v>100</v>
       </c>
       <c r="K25" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="3">
         <v>100</v>
       </c>
       <c r="M25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="1">
         <v>0</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>81</v>
+        <v>1003</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
@@ -5426,36 +5426,36 @@
         <v>100</v>
       </c>
       <c r="K26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" s="3">
         <v>100</v>
       </c>
       <c r="M26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" s="1">
         <v>0</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>82</v>
+        <v>1004</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
@@ -5467,36 +5467,36 @@
         <v>100</v>
       </c>
       <c r="K27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="3">
         <v>100</v>
       </c>
       <c r="M27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="E28" s="1">
-        <v>83</v>
+        <v>1005</v>
       </c>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G28" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
@@ -5508,36 +5508,36 @@
         <v>100</v>
       </c>
       <c r="K28" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="3">
         <v>100</v>
       </c>
       <c r="M28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
       <c r="E29" s="1">
-        <v>84</v>
+        <v>1006</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
@@ -5549,36 +5549,36 @@
         <v>100</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>100</v>
       </c>
       <c r="M29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
       <c r="E30" s="1">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="F30" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
@@ -5590,7 +5590,7 @@
         <v>100</v>
       </c>
       <c r="K30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" s="3">
         <v>100</v>
@@ -5599,21 +5599,21 @@
         <v>1</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="E31" s="1">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F31" s="1">
         <v>10</v>
@@ -5631,7 +5631,7 @@
         <v>100</v>
       </c>
       <c r="K31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="3">
         <v>100</v>
@@ -5640,27 +5640,27 @@
         <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="1">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
       <c r="E32" s="1">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="F32" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
@@ -5672,7 +5672,7 @@
         <v>100</v>
       </c>
       <c r="K32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
@@ -5681,255 +5681,9 @@
         <v>1</v>
       </c>
       <c r="N32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C33" s="1">
-        <v>1115</v>
-      </c>
-      <c r="D33" s="1">
-        <v>2</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1004</v>
-      </c>
-      <c r="F33" s="1">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1">
-        <v>50</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
-      <c r="J33" s="1">
-        <v>100</v>
-      </c>
-      <c r="K33" s="1">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3">
-        <v>100</v>
-      </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-      <c r="N33" s="1">
-        <v>1</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="1">
-        <v>1116</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1005</v>
-      </c>
-      <c r="F34" s="1">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1">
-        <v>50</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="1">
-        <v>1</v>
-      </c>
-      <c r="J34" s="1">
-        <v>100</v>
-      </c>
-      <c r="K34" s="1">
-        <v>3</v>
-      </c>
-      <c r="L34" s="3">
-        <v>100</v>
-      </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-      <c r="N34" s="1">
-        <v>2</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1">
-        <v>1117</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1006</v>
-      </c>
-      <c r="F35" s="1">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1">
-        <v>50</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1">
-        <v>100</v>
-      </c>
-      <c r="K35" s="1">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
-        <v>100</v>
-      </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-      <c r="N35" s="1">
-        <v>3</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C36" s="1">
-        <v>1118</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1007</v>
-      </c>
-      <c r="F36" s="1">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1">
-        <v>50</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="1">
-        <v>100</v>
-      </c>
-      <c r="K36" s="1">
-        <v>2</v>
-      </c>
-      <c r="L36" s="3">
-        <v>100</v>
-      </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-      <c r="N36" s="1">
-        <v>1</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C37" s="1">
-        <v>1119</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1008</v>
-      </c>
-      <c r="F37" s="1">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1">
-        <v>50</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="J37" s="1">
-        <v>100</v>
-      </c>
-      <c r="K37" s="1">
-        <v>2</v>
-      </c>
-      <c r="L37" s="3">
-        <v>100</v>
-      </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
-      <c r="N37" s="1">
-        <v>2</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C38" s="1">
-        <v>1120</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1009</v>
-      </c>
-      <c r="F38" s="1">
-        <v>10</v>
-      </c>
-      <c r="G38" s="1">
-        <v>50</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="1">
-        <v>100</v>
-      </c>
-      <c r="K38" s="1">
-        <v>2</v>
-      </c>
-      <c r="L38" s="3">
-        <v>100</v>
-      </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1">
-        <v>3</v>
-      </c>
-      <c r="O38" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -6093,7 +5847,7 @@
         <v>10001</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>21000</v>
@@ -6134,7 +5888,7 @@
         <v>10002</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>21001</v>
@@ -6175,7 +5929,7 @@
         <v>10003</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>21002</v>
@@ -6216,7 +5970,7 @@
         <v>10004</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>21003</v>
@@ -6257,7 +6011,7 @@
         <v>10005</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>21004</v>
@@ -6298,7 +6052,7 @@
         <v>10006</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>21005</v>
@@ -6339,7 +6093,7 @@
         <v>10007</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>21006</v>
@@ -6380,7 +6134,7 @@
         <v>10008</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>21007</v>
@@ -6421,7 +6175,7 @@
         <v>10009</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>22001</v>
@@ -6462,7 +6216,7 @@
         <v>10010</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>22002</v>
@@ -6503,7 +6257,7 @@
         <v>10011</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>22003</v>
@@ -6544,7 +6298,7 @@
         <v>10012</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>22004</v>
@@ -6585,7 +6339,7 @@
         <v>10013</v>
       </c>
       <c r="D18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>22005</v>
@@ -6626,7 +6380,7 @@
         <v>10014</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>22006</v>
@@ -6667,7 +6421,7 @@
         <v>10015</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>22007</v>
@@ -6708,7 +6462,7 @@
         <v>10016</v>
       </c>
       <c r="D21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
         <v>23001</v>
@@ -6749,7 +6503,7 @@
         <v>10017</v>
       </c>
       <c r="D22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>23002</v>
@@ -6790,7 +6544,7 @@
         <v>10018</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
         <v>23003</v>
@@ -6831,7 +6585,7 @@
         <v>10019</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
         <v>23004</v>
@@ -6872,7 +6626,7 @@
         <v>10020</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
         <v>23005</v>
@@ -6913,7 +6667,7 @@
         <v>10021</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
         <v>23006</v>
@@ -6954,7 +6708,7 @@
         <v>10022</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
         <v>23007</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -232,7 +232,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -400,6 +400,24 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>1,3,7</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>4,5,10</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
   </si>
   <si>
     <t>全技能等级增加</t>
@@ -4516,7 +4534,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O32"/>
+  <dimension ref="C1:O35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -4887,7 +4905,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J13" s="1">
         <v>100</v>
@@ -4928,7 +4946,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1">
         <v>100</v>
@@ -4969,7 +4987,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1">
         <v>100</v>
@@ -5010,7 +5028,7 @@
         <v>55</v>
       </c>
       <c r="I16" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1">
         <v>100</v>
@@ -5051,7 +5069,7 @@
         <v>53</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J17" s="1">
         <v>100</v>
@@ -5092,7 +5110,7 @@
         <v>54</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J18" s="1">
         <v>100</v>
@@ -5133,7 +5151,7 @@
         <v>52</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J19" s="1">
         <v>100</v>
@@ -5174,7 +5192,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J20" s="1">
         <v>100</v>
@@ -5215,7 +5233,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J21" s="1">
         <v>100</v>
@@ -5256,7 +5274,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J22" s="1">
         <v>100</v>
@@ -5297,7 +5315,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J23" s="1">
         <v>100</v>
@@ -5338,7 +5356,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J24" s="1">
         <v>100</v>
@@ -5379,7 +5397,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J25" s="1">
         <v>100</v>
@@ -5420,7 +5438,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J26" s="1">
         <v>100</v>
@@ -5461,7 +5479,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J27" s="1">
         <v>100</v>
@@ -5502,7 +5520,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J28" s="1">
         <v>100</v>
@@ -5543,7 +5561,7 @@
         <v>30</v>
       </c>
       <c r="I29" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J29" s="1">
         <v>100</v>
@@ -5584,7 +5602,7 @@
         <v>30</v>
       </c>
       <c r="I30" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J30" s="1">
         <v>100</v>
@@ -5625,7 +5643,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J31" s="1">
         <v>100</v>
@@ -5666,7 +5684,7 @@
         <v>30</v>
       </c>
       <c r="I32" s="1">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J32" s="1">
         <v>100</v>
@@ -5685,6 +5703,129 @@
       </c>
       <c r="O32" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:15">
+      <c r="C33" s="1">
+        <v>1121</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10003</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" s="1">
+        <v>60</v>
+      </c>
+      <c r="J33" s="1">
+        <v>100</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>40</v>
+      </c>
+      <c r="M33" s="1">
+        <v>2</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:15">
+      <c r="C34" s="1">
+        <v>1122</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>10002</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="1">
+        <v>60</v>
+      </c>
+      <c r="J34" s="1">
+        <v>100</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>40</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:15">
+      <c r="C35" s="1">
+        <v>1123</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10001</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" s="1">
+        <v>60</v>
+      </c>
+      <c r="J35" s="1">
+        <v>100</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>40</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5880,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -5921,7 +6062,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -5962,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6003,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6044,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6085,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6126,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6167,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6208,7 +6349,7 @@
         <v>2</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
@@ -6249,7 +6390,7 @@
         <v>2</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="3:15">
@@ -6290,7 +6431,7 @@
         <v>2</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="3:15">
@@ -6331,7 +6472,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="3:15">
@@ -6372,7 +6513,7 @@
         <v>2</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="3:15">
@@ -6413,7 +6554,7 @@
         <v>2</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="3:15">
@@ -6454,7 +6595,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="3:15">
@@ -6495,7 +6636,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="3:15">
@@ -6536,7 +6677,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="3:15">
@@ -6577,7 +6718,7 @@
         <v>3</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="3:15">
@@ -6618,7 +6759,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="3:15">
@@ -6659,7 +6800,7 @@
         <v>3</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="3:15">
@@ -6700,7 +6841,7 @@
         <v>3</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="3:15">
@@ -6741,7 +6882,7 @@
         <v>3</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -662,12 +662,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4691,7 +4691,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
         <v>20</v>
@@ -4732,7 +4732,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>
@@ -5347,7 +5347,7 @@
         <v>1001</v>
       </c>
       <c r="F24" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1">
         <v>100</v>
@@ -5388,7 +5388,7 @@
         <v>1002</v>
       </c>
       <c r="F25" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" s="1">
         <v>50</v>
@@ -5429,7 +5429,7 @@
         <v>1003</v>
       </c>
       <c r="F26" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1">
         <v>30</v>
@@ -5470,7 +5470,7 @@
         <v>1004</v>
       </c>
       <c r="F27" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1">
         <v>50</v>
@@ -5511,7 +5511,7 @@
         <v>1005</v>
       </c>
       <c r="F28" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
         <v>50</v>
@@ -5552,7 +5552,7 @@
         <v>1006</v>
       </c>
       <c r="F29" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1">
         <v>50</v>
@@ -5593,7 +5593,7 @@
         <v>1007</v>
       </c>
       <c r="F30" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
         <v>50</v>
@@ -5634,7 +5634,7 @@
         <v>1008</v>
       </c>
       <c r="F31" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1">
         <v>50</v>
@@ -5675,7 +5675,7 @@
         <v>1009</v>
       </c>
       <c r="F32" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1">
         <v>50</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -662,12 +662,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -4811,7 +4811,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1">
         <v>5</v>
